--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2022.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Migración interna neta</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2022.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:21</t>
+    <t xml:space="preserve">2026-07-30 15:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2185,16 +2185,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_m_miginterna_a_2022.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Migracion interna neta</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13647,23 +13656,23 @@
         <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -13685,21 +13694,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13708,7 +13717,7 @@
         <v>2022</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2022.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (por 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">Aysen</t>
@@ -427,18 +427,18 @@
     <t xml:space="preserve">La Cruz</t>
   </si>
   <si>
+    <t xml:space="preserve">13130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
     <t xml:space="preserve">6104</t>
   </si>
   <si>
     <t xml:space="preserve">Coltauco</t>
   </si>
   <si>
-    <t xml:space="preserve">13130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Miguel</t>
-  </si>
-  <si>
     <t xml:space="preserve">6308</t>
   </si>
   <si>
@@ -733,36 +733,36 @@
     <t xml:space="preserve">Olivar</t>
   </si>
   <si>
+    <t xml:space="preserve">6117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Vicente</t>
+  </si>
+  <si>
     <t xml:space="preserve">7202</t>
   </si>
   <si>
     <t xml:space="preserve">Chanco</t>
   </si>
   <si>
-    <t xml:space="preserve">6117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Vicente</t>
-  </si>
-  <si>
     <t xml:space="preserve">16203</t>
   </si>
   <si>
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
+    <t xml:space="preserve">5601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
     <t xml:space="preserve">7308</t>
   </si>
   <si>
     <t xml:space="preserve">Teno</t>
   </si>
   <si>
-    <t xml:space="preserve">5601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
     <t xml:space="preserve">13109</t>
   </si>
   <si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:28</t>
+    <t xml:space="preserve">2026-09-08 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2590,9 +2590,9 @@
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4488,10 +4488,10 @@
         <v>2022</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>136</v>
@@ -4520,10 +4520,10 @@
         <v>2022</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>138</v>
@@ -6120,10 +6120,10 @@
         <v>2022</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>238</v>
@@ -6152,10 +6152,10 @@
         <v>2022</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>240</v>
@@ -6216,10 +6216,10 @@
         <v>2022</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>244</v>
@@ -6248,10 +6248,10 @@
         <v>2022</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>246</v>
@@ -13687,7 +13687,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
